--- a/output/pdf_financials_xlsx/CBR.xlsx
+++ b/output/pdf_financials_xlsx/CBR.xlsx
@@ -1015,19 +1015,19 @@
         <v>-1.419562</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.28738</v>
+        <v>-0.28738</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>2.622713</v>
+        <v>-2.622713</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>3.20366</v>
+        <v>-3.20366</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>4.298114</v>
+        <v>-4.298114</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>11.205185</v>
+        <v>-11.205185</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>10.346633</v>
@@ -1216,22 +1216,22 @@
         <v>-0.147399</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1.304738</v>
+        <v>-1.304738</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.28738</v>
+        <v>-0.28738</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>2.622713</v>
+        <v>-2.622713</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>3.20366</v>
+        <v>-3.20366</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>4.298114</v>
+        <v>-4.298114</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>11.205185</v>
+        <v>-11.205185</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>10.346633</v>
@@ -1336,22 +1336,22 @@
         <v>-0.147399</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1.304738</v>
+        <v>-1.304738</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.28738</v>
+        <v>-0.28738</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>2.622713</v>
+        <v>-2.622713</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>3.20366</v>
+        <v>-3.20366</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>4.298114</v>
+        <v>-4.298114</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>11.205185</v>
+        <v>-11.205185</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>10.346633</v>
@@ -1456,10 +1456,10 @@
         <v>2.45665</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-16.309225</v>
+        <v>16.309225</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-0.350463</v>
+        <v>0.350463</v>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
@@ -1467,13 +1467,13 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>32.0366</v>
+        <v>-32.0366</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>47.756822</v>
+        <v>-47.756822</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>124.502056</v>
+        <v>-124.502056</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>147.484351</v>
@@ -1501,19 +1501,19 @@
         <v>-1.419562</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.28738</v>
+        <v>-0.28738</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>2.622713</v>
+        <v>-2.622713</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3.20366</v>
+        <v>-3.20366</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>4.298114</v>
+        <v>-4.298114</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>11.205185</v>
+        <v>-11.205185</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>10.346633</v>
@@ -1581,19 +1581,19 @@
         <v>-1.419562</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.291336</v>
+        <v>-0.283424</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>2.63098</v>
+        <v>-2.614446</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>3.270125</v>
+        <v>-3.137195</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>4.406727</v>
+        <v>-4.189501</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>11.577552</v>
+        <v>-10.832818</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>10.9765</v>
@@ -1683,19 +1683,19 @@
         <v>-8.088692145887252</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>0</v>
@@ -4182,13 +4182,13 @@
         <v>0</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>7.047795</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>7.01128</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>8.219728999999999</v>
       </c>
     </row>
     <row r="93">
@@ -4417,13 +4417,13 @@
         <v>0.090393</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>3.20366</v>
+        <v>-3.20366</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>4.298114</v>
+        <v>-4.298114</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>11.205185</v>
+        <v>-11.205185</v>
       </c>
       <c r="I99" s="3" t="n">
         <v>10.346633</v>
@@ -6849,7 +6849,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -29694,19 +29698,19 @@
         </is>
       </c>
       <c r="H342" s="5" t="n">
-        <v>2.622713</v>
+        <v>-2.622713</v>
       </c>
       <c r="I342" s="5" t="n">
-        <v>3.20366</v>
+        <v>-3.20366</v>
       </c>
       <c r="J342" s="5" t="n">
-        <v>4.298114</v>
+        <v>-4.298114</v>
       </c>
       <c r="K342" s="5" t="n">
-        <v>11.205185</v>
+        <v>-11.205185</v>
       </c>
       <c r="L342" s="5" t="n">
-        <v>10.346633</v>
+        <v>-10.346633</v>
       </c>
       <c r="M342" t="inlineStr">
         <is>
@@ -29845,10 +29849,10 @@
         </is>
       </c>
       <c r="K344" s="5" t="n">
-        <v>11.517514</v>
+        <v>-11.517514</v>
       </c>
       <c r="L344" s="5" t="n">
-        <v>9.785857999999999</v>
+        <v>-9.785857999999999</v>
       </c>
       <c r="M344" t="inlineStr">
         <is>
@@ -31717,13 +31721,13 @@
         </is>
       </c>
       <c r="H371" s="5" t="n">
-        <v>2.738451</v>
+        <v>-2.738451</v>
       </c>
       <c r="I371" s="5" t="n">
-        <v>3.299879</v>
+        <v>-3.299879</v>
       </c>
       <c r="J371" s="5" t="n">
-        <v>4.450122</v>
+        <v>-4.450122</v>
       </c>
       <c r="K371" t="inlineStr">
         <is>
@@ -34384,10 +34388,10 @@
         </is>
       </c>
       <c r="G409" s="5" t="n">
-        <v>0.28738</v>
+        <v>-0.28738</v>
       </c>
       <c r="H409" s="5" t="n">
-        <v>2.622713</v>
+        <v>-2.622713</v>
       </c>
       <c r="I409" t="inlineStr">
         <is>
@@ -34457,10 +34461,10 @@
         </is>
       </c>
       <c r="G410" s="5" t="n">
-        <v>0.261986</v>
+        <v>-0.261986</v>
       </c>
       <c r="H410" s="5" t="n">
-        <v>2.738451</v>
+        <v>-2.738451</v>
       </c>
       <c r="I410" t="inlineStr">
         <is>
@@ -36884,7 +36888,7 @@
         </is>
       </c>
       <c r="F444" s="5" t="n">
-        <v>1.213139</v>
+        <v>-1.213139</v>
       </c>
       <c r="G444" s="5" t="n">
         <v>-2.427231</v>
@@ -39012,10 +39016,10 @@
         </is>
       </c>
       <c r="F474" s="5" t="n">
-        <v>1.304738</v>
+        <v>-1.304738</v>
       </c>
       <c r="G474" s="5" t="n">
-        <v>2.526737</v>
+        <v>-2.526737</v>
       </c>
       <c r="H474" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/CBR.xlsx
+++ b/output/pdf_financials_xlsx/CBR.xlsx
@@ -855,31 +855,31 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000793</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.012129</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.022816</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.018316</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.042561</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.048774</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.140916</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.08158700000000001</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.142075</v>
       </c>
     </row>
     <row r="13">
@@ -1501,31 +1501,31 @@
         <v>-1.419562</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.28738</v>
+        <v>-0.286587</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.622713</v>
+        <v>-2.610584</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-3.20366</v>
+        <v>-3.180844</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-4.298114</v>
+        <v>-4.279798</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-11.205185</v>
+        <v>-11.162624</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>10.346633</v>
+        <v>10.395407</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>1.124681</v>
+        <v>0.983765</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-7.27601</v>
+        <v>-7.357597</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-11.500021</v>
+        <v>-11.642096</v>
       </c>
     </row>
     <row r="28">
@@ -1581,31 +1581,31 @@
         <v>-1.419562</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.283424</v>
+        <v>-0.282631</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.614446</v>
+        <v>-2.602317</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-3.137195</v>
+        <v>-3.114379</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-4.189501</v>
+        <v>-4.171185</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-10.832818</v>
+        <v>-10.790257</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>10.9765</v>
+        <v>11.025274</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>1.781487</v>
+        <v>1.640571</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-6.697578</v>
+        <v>-6.779165</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-11.403323</v>
+        <v>-11.545398</v>
       </c>
     </row>
     <row r="30">
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.060246</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.190955</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>2.184746</v>
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.060246</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.25</v>
+        <v>0.440955</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>2.184746</v>
@@ -2346,10 +2346,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.255999</v>
+        <v>1.195753</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.669048</v>
+        <v>1.478093</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.010994</v>
@@ -10020,7 +10020,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">
@@ -24813,7 +24813,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -28421,7 +28421,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -28630,7 +28630,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -36167,7 +36167,7 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
@@ -36386,7 +36386,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">

--- a/output/pdf_financials_xlsx/CBR.xlsx
+++ b/output/pdf_financials_xlsx/CBR.xlsx
@@ -3032,13 +3032,13 @@
         <v>0</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.19047</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>0.221109</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>1.099435</v>
       </c>
     </row>
     <row r="65">
@@ -4848,10 +4848,10 @@
         <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.150394</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.07538300000000001</v>
       </c>
       <c r="E110" s="3" t="n">
         <v>0</v>
@@ -4885,10 +4885,10 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.013434</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.06973799999999999</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -5827,10 +5827,10 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.013434</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.06973799999999999</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -5867,10 +5867,10 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-0.049721</v>
+        <v>-0.063155</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-1.219349</v>
+        <v>-1.289087</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>-0.277475</v>
@@ -19334,7 +19334,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -21411,7 +21415,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E224" s="5" t="n">
         <v>-0.013434</v>
       </c>
@@ -22476,7 +22484,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr"/>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr">
         <is>
           <t>-</t>
